--- a/input_data/admin_data/CRI/diverse_CRI_2010.xlsx
+++ b/input_data/admin_data/CRI/diverse_CRI_2010.xlsx
@@ -242,7 +242,7 @@
         <v>0.036165580153465271</v>
       </c>
       <c r="J6">
-        <v>5.0934524536132812</v>
+        <v>5.0934524536132813</v>
       </c>
     </row>
     <row r="7">

--- a/input_data/admin_data/CRI/diverse_CRI_2010.xlsx
+++ b/input_data/admin_data/CRI/diverse_CRI_2010.xlsx
@@ -242,7 +242,7 @@
         <v>0.036165580153465271</v>
       </c>
       <c r="J6">
-        <v>5.0934524536132813</v>
+        <v>5.0934524536132812</v>
       </c>
     </row>
     <row r="7">
